--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jun-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jun-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>77199.2</v>
+        <v>78303.85000000001</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>354.22</v>
+        <v>359.29</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1660.42</v>
+        <v>1684.18</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9477.030000000001</v>
+        <v>9612.639999999999</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>11921.79</v>
+        <v>12092.38</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>24352.87</v>
+        <v>24701.34</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>630.96</v>
+        <v>639.99</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>48.71</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>36673.11</v>
+        <v>37197.87</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10789.43</v>
+        <v>10943.81</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>15564.23</v>
+        <v>15786.94</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>97.41</v>
+        <v>98.81</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6175.98</v>
+        <v>6248.43</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1266.22</v>
+        <v>1281.07</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7028.9</v>
+        <v>7111.36</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6750.62</v>
+        <v>6829.8</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>46491.84</v>
+        <v>47037.22</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>26386.15</v>
+        <v>26695.67</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2776.23</v>
+        <v>2808.79</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>423.74</v>
+        <v>428.71</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3926.68</v>
+        <v>3972.74</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>36278.16</v>
+        <v>36703.72</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>77486.41</v>
+        <v>78395.37</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>24708.42</v>
+        <v>25126.3</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>153341.65</v>
+        <v>155935.02</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>21180.93</v>
+        <v>21539.15</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>14567.62</v>
+        <v>14813.99</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>58118.77</v>
+        <v>59101.7</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>625.7</v>
+        <v>636.28</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8810.629999999999</v>
+        <v>8959.639999999999</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>12619.21</v>
+        <v>12832.64</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>886.71</v>
+        <v>901.71</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1217.64</v>
+        <v>1238.24</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1839.66</v>
+        <v>1870.77</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1941.26</v>
+        <v>1974.09</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>13283.38</v>
+        <v>13508.04</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5803.34</v>
+        <v>5901.48</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>8365.49</v>
+        <v>8506.969999999999</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2479.45</v>
+        <v>2521.39</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>10789.43</v>
+        <v>10971.9</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>13283.38</v>
+        <v>13508.04</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>14732.3</v>
+        <v>14981.46</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>7627.32</v>
+        <v>7704.88</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>885.5599999999999</v>
+        <v>894.5599999999999</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>15016.86</v>
+        <v>15169.58</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1631.64</v>
+        <v>1648.23</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>78870.09</v>
+        <v>79672.14</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>683.54</v>
+        <v>690.49</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>769.77</v>
+        <v>777.6</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>13284.42</v>
+        <v>13419.51</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>337.56</v>
+        <v>341</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2641.97</v>
+        <v>2668.83</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>498.46</v>
+        <v>503.53</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1375.04</v>
+        <v>1389.02</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>7748.64</v>
+        <v>7827.44</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>577.33</v>
+        <v>582.74</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>32876.37</v>
+        <v>33184.73</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>18928.82</v>
+        <v>19106.36</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1169.38</v>
+        <v>1180.35</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5151.79</v>
+        <v>5200.11</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>981.14</v>
+        <v>990.35</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>25847.1</v>
+        <v>26089.52</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>12514.05</v>
+        <v>12631.43</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>46816.76</v>
+        <v>47255.86</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>9054.290000000001</v>
+        <v>9139.209999999999</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1660.42</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2100.05</v>
+        <v>2119.74</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>25028.11</v>
+        <v>24838.24</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>36110.38</v>
+        <v>35836.44</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>4109.66</v>
+        <v>4078.48</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>399.83</v>
+        <v>396.8</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>5508.29</v>
+        <v>5466.5</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>15272.4</v>
+        <v>15156.54</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>61840.46</v>
+        <v>61371.32</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>788.24</v>
+        <v>782.26</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>22083.63</v>
+        <v>21916.09</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>51100.11</v>
+        <v>50712.45</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>604.67</v>
+        <v>594.45</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>977.26</v>
+        <v>960.75</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>26902.84</v>
+        <v>26448.29</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>5005.62</v>
+        <v>4921.05</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>73612.08</v>
+        <v>72368.35000000001</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2258.16</v>
+        <v>2220.01</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>29096.96</v>
+        <v>28605.35</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>42828.14</v>
+        <v>42104.53</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1217.64</v>
+        <v>1197.07</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2806.86</v>
+        <v>2759.44</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>16941.29</v>
+        <v>16655.06</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>496.8</v>
+        <v>488.4</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>11701.69</v>
+        <v>11535.62</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3320.84</v>
+        <v>3273.71</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1062.67</v>
+        <v>1047.59</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>974.83</v>
+        <v>961</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>22004.76</v>
+        <v>21692.46</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>841.28</v>
+        <v>829.34</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3320.85</v>
+        <v>3273.72</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>77265.00999999999</v>
+        <v>76168.44</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>6507.31</v>
+        <v>6414.95</v>
       </c>
     </row>
     <row r="100">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>211933.44</v>
+        <v>208925.61</v>
       </c>
     </row>
     <row r="101">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>5840.07</v>
+        <v>5757.18</v>
       </c>
     </row>
     <row r="102">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>6641.69</v>
+        <v>6547.43</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>14391.16</v>
+        <v>14193.42</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>9420.24</v>
+        <v>9290.809999999999</v>
       </c>
     </row>
     <row r="105">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>15090.48</v>
+        <v>14883.13</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>176.67</v>
+        <v>174.24</v>
       </c>
     </row>
     <row r="107">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>14675.09</v>
+        <v>14473.45</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>208.22</v>
+        <v>205.36</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>5067.88</v>
+        <v>4998.24</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>13729.71</v>
+        <v>13541.06</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>13774.14</v>
+        <v>13584.88</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>227.15</v>
+        <v>224.02</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>14074.08</v>
+        <v>13880.7</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>6840.88</v>
+        <v>6746.88</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>7767.13</v>
+        <v>7660.4</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>4963.45</v>
+        <v>4895.25</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>6989.09</v>
+        <v>6893.06</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>18771.08</v>
+        <v>18654.71</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>27992.57</v>
+        <v>27819.02</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3673.58</v>
+        <v>3650.81</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>7092</v>
+        <v>7048.03</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>77486.39999999999</v>
+        <v>77006.00999999999</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>905.4299999999999</v>
+        <v>899.8099999999999</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>99.63</v>
+        <v>99.01000000000001</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>12751.16</v>
+        <v>12672.11</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>9948.9</v>
+        <v>9887.219999999999</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>12145.99</v>
+        <v>12070.69</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>24522.29</v>
+        <v>24370.26</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>876.7</v>
+        <v>871.27</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>28554.96</v>
+        <v>28377.93</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>26057.57</v>
+        <v>25896.02</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>26057.57</v>
+        <v>25896.02</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>225.82</v>
+        <v>224.42</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>6143.56</v>
+        <v>6105.48</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>4204.83</v>
+        <v>4223.92</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>37571.61</v>
+        <v>37742.24</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>10514.96</v>
+        <v>10562.72</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>8855.59</v>
+        <v>8895.809999999999</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>75.72</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>43170.98</v>
+        <v>43367.05</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>3104.33</v>
+        <v>3118.43</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>81649.47</v>
+        <v>82020.28999999999</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>74347.14999999999</v>
+        <v>74684.81</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>10199.48</v>
+        <v>10245.8</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>31697.36</v>
+        <v>31841.32</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>14977.02</v>
+        <v>15045.04</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>16603.65</v>
+        <v>16679.05</v>
       </c>
     </row>
     <row r="148">
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>730426.95</v>
+        <v>741303.22</v>
       </c>
     </row>
     <row r="149">
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>322.3</v>
+        <v>327.09</v>
       </c>
     </row>
     <row r="150">
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1660.42</v>
+        <v>1685.15</v>
       </c>
     </row>
     <row r="151">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>3311.99</v>
+        <v>3361.31</v>
       </c>
     </row>
     <row r="152">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>276.16</v>
+        <v>280.27</v>
       </c>
     </row>
     <row r="153">
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>77486.39999999999</v>
+        <v>78640.2</v>
       </c>
     </row>
     <row r="154">
@@ -9849,7 +9849,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>21917.58</v>
+        <v>22243.94</v>
       </c>
     </row>
     <row r="155">
@@ -9914,7 +9914,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>110418.12</v>
+        <v>112062.28</v>
       </c>
     </row>
     <row r="156">
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>276.16</v>
+        <v>280.27</v>
       </c>
     </row>
     <row r="157">
@@ -10036,7 +10036,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2337.88</v>
+        <v>2372.69</v>
       </c>
     </row>
     <row r="158">
@@ -10097,7 +10097,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>8759.84</v>
+        <v>8926.379999999999</v>
       </c>
     </row>
     <row r="159">
@@ -10158,7 +10158,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>315.48</v>
+        <v>321.48</v>
       </c>
     </row>
     <row r="160">
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1865.29</v>
+        <v>1900.75</v>
       </c>
     </row>
     <row r="161">
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>10253.11</v>
+        <v>10448.04</v>
       </c>
     </row>
     <row r="162">
@@ -10341,7 +10341,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2291.06</v>
+        <v>2334.62</v>
       </c>
     </row>
     <row r="163">
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>409.13</v>
+        <v>416.91</v>
       </c>
     </row>
     <row r="164">
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>423.74</v>
+        <v>431.8</v>
       </c>
     </row>
     <row r="165">
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>32316.66</v>
+        <v>32931.05</v>
       </c>
     </row>
     <row r="166">
@@ -10585,7 +10585,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>14465.6</v>
+        <v>14740.62</v>
       </c>
     </row>
     <row r="167">
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>9962.540000000001</v>
+        <v>10151.94</v>
       </c>
     </row>
     <row r="168">
@@ -10707,7 +10707,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>774.86</v>
+        <v>789.6</v>
       </c>
     </row>
     <row r="169">
@@ -10768,7 +10768,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>19925.07</v>
+        <v>20303.88</v>
       </c>
     </row>
     <row r="170">
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>38743.2</v>
+        <v>39479.77</v>
       </c>
     </row>
     <row r="171">
@@ -10890,7 +10890,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>42051.43</v>
+        <v>42850.89</v>
       </c>
     </row>
     <row r="172">
@@ -10951,7 +10951,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>5620.64</v>
+        <v>5727.5</v>
       </c>
     </row>
     <row r="173">
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>26404.65</v>
+        <v>26906.65</v>
       </c>
     </row>
     <row r="174">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1992.24</v>
+        <v>2030.11</v>
       </c>
     </row>
     <row r="175">
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>385.73</v>
+        <v>393.06</v>
       </c>
     </row>
     <row r="176">
@@ -11195,7 +11195,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1051.6</v>
+        <v>1075.32</v>
       </c>
     </row>
     <row r="177">
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1156.76</v>
+        <v>1182.85</v>
       </c>
     </row>
     <row r="178">
@@ -11317,7 +11317,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>61318.87</v>
+        <v>62701.76</v>
       </c>
     </row>
     <row r="179">
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>836.85</v>
+        <v>855.73</v>
       </c>
     </row>
     <row r="180">
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1240.11</v>
+        <v>1268.08</v>
       </c>
     </row>
     <row r="181">
@@ -11500,7 +11500,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>17731.79</v>
+        <v>18131.68</v>
       </c>
     </row>
     <row r="182">
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>9426.549999999999</v>
+        <v>9639.15</v>
       </c>
     </row>
     <row r="183">
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2213.9</v>
+        <v>2263.83</v>
       </c>
     </row>
     <row r="184">
@@ -11683,7 +11683,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>241.93</v>
+        <v>247.38</v>
       </c>
     </row>
     <row r="185">
@@ -11744,7 +11744,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>410995.54</v>
+        <v>420264.55</v>
       </c>
     </row>
     <row r="186">
@@ -11805,7 +11805,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>4029.29</v>
+        <v>4120.16</v>
       </c>
     </row>
     <row r="187">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>3243.8</v>
+        <v>3316.96</v>
       </c>
     </row>
     <row r="188">
@@ -11927,7 +11927,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>60624.03</v>
+        <v>61991.26</v>
       </c>
     </row>
     <row r="189">
@@ -11988,7 +11988,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>159.84</v>
+        <v>163.45</v>
       </c>
     </row>
     <row r="190">
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>974.11</v>
+        <v>996.08</v>
       </c>
     </row>
     <row r="191">
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>553.5</v>
+        <v>565.98</v>
       </c>
     </row>
     <row r="192">
@@ -12171,7 +12171,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>5136.24</v>
+        <v>5252.08</v>
       </c>
     </row>
     <row r="193">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>29886.09</v>
+        <v>30092.43</v>
       </c>
     </row>
     <row r="194">
@@ -12293,7 +12293,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>27737.03</v>
+        <v>27928.53</v>
       </c>
     </row>
     <row r="195">
@@ -12354,7 +12354,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>36344.7</v>
+        <v>36595.63</v>
       </c>
     </row>
     <row r="196">
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>115676.13</v>
+        <v>116474.77</v>
       </c>
     </row>
     <row r="197">
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>276.74</v>
+        <v>278.65</v>
       </c>
     </row>
     <row r="198">
@@ -12537,7 +12537,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3320.84</v>
+        <v>3343.77</v>
       </c>
     </row>
     <row r="199">
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>504.77</v>
+        <v>508.25</v>
       </c>
     </row>
     <row r="200">
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>8958.77</v>
+        <v>9020.620000000001</v>
       </c>
     </row>
     <row r="201">
@@ -12720,7 +12720,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>67594.71000000001</v>
+        <v>68061.39</v>
       </c>
     </row>
     <row r="202">
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>40608.41</v>
+        <v>40888.77</v>
       </c>
     </row>
     <row r="203">
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>547.9400000000001</v>
+        <v>551.72</v>
       </c>
     </row>
     <row r="204">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>14221.85</v>
+        <v>14320.04</v>
       </c>
     </row>
     <row r="205">
@@ -12964,7 +12964,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2939.6</v>
+        <v>2959.89</v>
       </c>
     </row>
     <row r="206">
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>14264.82</v>
+        <v>14363.31</v>
       </c>
     </row>
     <row r="207">
@@ -13086,7 +13086,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>664.17</v>
+        <v>666.22</v>
       </c>
     </row>
     <row r="208">
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>5050.21</v>
+        <v>5065.82</v>
       </c>
     </row>
     <row r="209">
@@ -13208,7 +13208,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1480.41</v>
+        <v>1484.99</v>
       </c>
     </row>
     <row r="210">
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>41494.43</v>
+        <v>41622.72</v>
       </c>
     </row>
     <row r="211">
@@ -13330,7 +13330,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>19885.54</v>
+        <v>19947.01</v>
       </c>
     </row>
     <row r="212">
@@ -13391,7 +13391,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>19925.08</v>
+        <v>19986.68</v>
       </c>
     </row>
     <row r="213">
@@ -13452,7 +13452,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>18745.51</v>
+        <v>18695.93</v>
       </c>
     </row>
     <row r="214">
@@ -13513,7 +13513,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>27063.83</v>
+        <v>26992.25</v>
       </c>
     </row>
     <row r="215">
@@ -13574,7 +13574,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>42728.48</v>
+        <v>42615.47</v>
       </c>
     </row>
     <row r="216">
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>14627.14</v>
+        <v>14588.45</v>
       </c>
     </row>
     <row r="217">
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>22139.34</v>
+        <v>22080.78</v>
       </c>
     </row>
     <row r="218">
@@ -13757,7 +13757,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>54240.48</v>
+        <v>54097.02</v>
       </c>
     </row>
     <row r="219">
@@ -13818,7 +13818,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>9023.99</v>
+        <v>9000.120000000001</v>
       </c>
     </row>
     <row r="220">
@@ -13879,7 +13879,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>21921.29</v>
+        <v>21863.31</v>
       </c>
     </row>
     <row r="221">
@@ -13940,7 +13940,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1817.83</v>
+        <v>1813.02</v>
       </c>
     </row>
     <row r="222">
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>16272.15</v>
+        <v>16229.11</v>
       </c>
     </row>
     <row r="223">
@@ -14062,7 +14062,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>13339.31</v>
+        <v>13304.02</v>
       </c>
     </row>
     <row r="224">
@@ -14123,7 +14123,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>19803.34</v>
+        <v>19750.96</v>
       </c>
     </row>
     <row r="225">
@@ -14184,7 +14184,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>56179.04</v>
+        <v>55430.72</v>
       </c>
     </row>
     <row r="226">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>52850.79</v>
+        <v>52146.81</v>
       </c>
     </row>
     <row r="227">
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>38743.2</v>
+        <v>38227.13</v>
       </c>
     </row>
     <row r="228">
@@ -14367,7 +14367,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>553.47</v>
+        <v>546.1</v>
       </c>
     </row>
     <row r="229">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>13283.6</v>
+        <v>13106.66</v>
       </c>
     </row>
     <row r="230">
@@ -14489,7 +14489,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>24353.08</v>
+        <v>23876.4</v>
       </c>
     </row>
     <row r="231">
@@ -14550,7 +14550,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>34427.08</v>
+        <v>33753.22</v>
       </c>
     </row>
     <row r="232">
@@ -14611,7 +14611,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>11715.95</v>
+        <v>11486.62</v>
       </c>
     </row>
     <row r="233">
@@ -14672,7 +14672,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>38645.26</v>
+        <v>37888.82</v>
       </c>
     </row>
     <row r="234">
@@ -14733,7 +14733,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>632.4400000000001</v>
+        <v>620.0599999999999</v>
       </c>
     </row>
     <row r="235">
@@ -14794,7 +14794,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>308.63</v>
+        <v>302.59</v>
       </c>
     </row>
     <row r="236">
@@ -14855,7 +14855,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>11455.59</v>
+        <v>11231.36</v>
       </c>
     </row>
     <row r="237">
@@ -14916,7 +14916,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>38530.11</v>
+        <v>37775.93</v>
       </c>
     </row>
     <row r="238">
@@ -14977,7 +14977,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>6845.12</v>
+        <v>6711.14</v>
       </c>
     </row>
     <row r="239">
@@ -15038,7 +15038,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>4127.08</v>
+        <v>4046.3</v>
       </c>
     </row>
     <row r="240">
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>9804.719999999999</v>
+        <v>9612.809999999999</v>
       </c>
     </row>
     <row r="241">
@@ -15160,7 +15160,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>18017.06</v>
+        <v>17664.4</v>
       </c>
     </row>
     <row r="242">
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>5496.75</v>
+        <v>5389.16</v>
       </c>
     </row>
     <row r="243">
@@ -15282,7 +15282,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>210.32</v>
+        <v>206.2</v>
       </c>
     </row>
     <row r="244">
@@ -15343,7 +15343,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>16604.23</v>
+        <v>16279.22</v>
       </c>
     </row>
     <row r="245">
@@ -15404,7 +15404,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>18818.13</v>
+        <v>18539.32</v>
       </c>
     </row>
     <row r="246">
@@ -15465,7 +15465,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>5534.74</v>
+        <v>5452.74</v>
       </c>
     </row>
     <row r="247">
@@ -15530,7 +15530,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>81986.28999999999</v>
+        <v>80771.59</v>
       </c>
     </row>
     <row r="248">
@@ -15591,7 +15591,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>35890.06</v>
+        <v>35358.32</v>
       </c>
     </row>
     <row r="249">
@@ -15652,7 +15652,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>9220.91</v>
+        <v>9084.299999999999</v>
       </c>
     </row>
     <row r="250">
@@ -15713,7 +15713,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>48976.3</v>
+        <v>48250.67</v>
       </c>
     </row>
     <row r="251">
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1771.12</v>
+        <v>1744.88</v>
       </c>
     </row>
     <row r="252">
@@ -15835,7 +15835,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>20761.2</v>
+        <v>20453.6</v>
       </c>
     </row>
     <row r="253">
@@ -15896,7 +15896,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>12577.28</v>
+        <v>12390.94</v>
       </c>
     </row>
     <row r="254">
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>21032.02</v>
+        <v>20720.42</v>
       </c>
     </row>
     <row r="255">
@@ -16018,7 +16018,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>24352.87</v>
+        <v>23992.06</v>
       </c>
     </row>
     <row r="256">
@@ -16079,7 +16079,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>111.95</v>
+        <v>109.65</v>
       </c>
     </row>
     <row r="257">
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>32273.09</v>
+        <v>31609.82</v>
       </c>
     </row>
     <row r="258">
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>11597.7</v>
+        <v>11359.35</v>
       </c>
     </row>
     <row r="259">
@@ -16262,7 +16262,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>65041.59</v>
+        <v>63704.87</v>
       </c>
     </row>
     <row r="260">
@@ -16323,7 +16323,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>17192.12</v>
+        <v>16838.79</v>
       </c>
     </row>
     <row r="261">
@@ -16384,7 +16384,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>5535.48</v>
+        <v>5421.72</v>
       </c>
     </row>
     <row r="262">
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>13296.51</v>
+        <v>13023.25</v>
       </c>
     </row>
     <row r="263">
@@ -16506,7 +16506,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>29843.11</v>
+        <v>29229.79</v>
       </c>
     </row>
     <row r="264">
@@ -16567,7 +16567,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>33208.46</v>
+        <v>32525.97</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jun-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jun-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15521,7 +15521,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -15754,7 +15754,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jun-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jun-2026.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SUBCENTRO DE TELECOMUNICACIONES NAVALES (V)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Centro de Referencia de Salud Hospital Provincia Cordillera</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SEREMI IX</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DIRECCION DE INFANCIA</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION VI REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE MAGALLANES</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación de Cachapoal</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Centro de Sangre y Tejidos de Concepcion</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>CORPORACIÓN DE FOMENTO DE LA PRODUCCIÓN - CORFO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DIRECTORIO DE TRANSPORTE DE SANTIAGO</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO CONTROL FINANCIERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Bienestar SSFFAA</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Bienestar SSFFAA</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Bienestar SSFFAA</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13366,7 +13366,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13549,7 +13549,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14159,7 +14159,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14281,7 +14281,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE FINANZAS DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14647,7 +14647,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14698,7 +14698,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Comité de Seguro Agricola</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>ARCHIVO NACIONAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16481,7 +16481,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jun-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M264"/>
+  <dimension ref="A1:M267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6788,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7337,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7899,7 +8379,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3323-73-CM26</t>
+          <t>5067-1490-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7924,12 +8404,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7947,14 +8427,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>899.8099999999999</v>
+        <v>9887.219999999999</v>
       </c>
     </row>
     <row r="124">
@@ -8008,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8082,7 +8574,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5067-1490-CM26</t>
+          <t>3323-73-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8107,12 +8599,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8130,14 +8622,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>9887.219999999999</v>
+        <v>899.8099999999999</v>
       </c>
     </row>
     <row r="127">
@@ -8191,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8509,7 +9029,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3326-364-CM26</t>
+          <t>1199-137-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8534,17 +9054,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8557,20 +9077,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>224.42</v>
+        <v>6105.48</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1199-137-CM26</t>
+          <t>3326-364-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8595,17 +9119,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8618,14 +9142,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>6105.48</v>
+        <v>224.42</v>
       </c>
     </row>
     <row r="135">
@@ -8679,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8801,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9106,7 +9662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9537,7 +10117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9598,7 +10182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9659,7 +10247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9720,7 +10312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9781,7 +10377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9842,7 +10442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9968,7 +10572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10029,7 +10637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10090,7 +10702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10151,7 +10767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10212,7 +10832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10273,7 +10897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10334,7 +10962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10395,7 +11027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10456,7 +11092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10517,7 +11157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10578,7 +11222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10639,7 +11287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10700,7 +11352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10761,7 +11417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10822,7 +11482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10883,7 +11547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10944,7 +11612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11005,7 +11677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11066,7 +11742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11127,7 +11807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11188,7 +11872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11249,7 +11937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11310,7 +12002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11371,7 +12067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11432,7 +12132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11493,7 +12197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11554,7 +12262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11615,7 +12327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11676,7 +12392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11737,7 +12457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11798,7 +12522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11859,7 +12587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11920,7 +12652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11981,7 +12717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12042,7 +12782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12103,7 +12847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12164,7 +12912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12225,7 +12977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12286,7 +13042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12347,7 +13107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12360,7 +13124,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1075956-7-CM26</t>
+          <t>4474-579-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12380,22 +13144,22 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>69.160.600-7</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12408,20 +13172,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>116474.77</v>
+        <v>278.65</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4474-579-CM26</t>
+          <t>5155-139-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12441,22 +13209,22 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>69.160.600-7</t>
+          <t>60.504.000-4</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12469,20 +13237,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>278.65</v>
+        <v>3343.77</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5155-139-CM26</t>
+          <t>1075956-7-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12507,12 +13279,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>60.504.000-4</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO ELECTORAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12530,14 +13302,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3343.77</v>
+        <v>116474.77</v>
       </c>
     </row>
     <row r="199">
@@ -12591,7 +13367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12604,7 +13384,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1057402-6716-CM26</t>
+          <t>1157285-7-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12629,17 +13409,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>62.000.860-5</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12652,14 +13432,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>9020.620000000001</v>
+        <v>40888.77</v>
       </c>
     </row>
     <row r="201">
@@ -12713,7 +13497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12726,7 +13514,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1157285-7-CM26</t>
+          <t>4106-10-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12746,17 +13534,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>62.000.860-5</t>
+          <t>65.480.540-7</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12774,20 +13562,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>40888.77</v>
+        <v>551.72</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>4106-10-CM26</t>
+          <t>1057402-6716-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12807,22 +13599,22 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>65.480.540-7</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12835,14 +13627,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>551.72</v>
+        <v>9020.620000000001</v>
       </c>
     </row>
     <row r="204">
@@ -12896,7 +13692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12957,7 +13757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13018,7 +13822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13079,7 +13887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13140,7 +13952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13201,7 +14017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13262,7 +14082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13323,7 +14147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13336,12 +14164,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2138-267-CM26</t>
+          <t>1077908-117-SE26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13361,17 +14189,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.978.730-7</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13384,20 +14212,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>19986.68</v>
+        <v>445747.94</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1079639-557-CM26</t>
+          <t>2138-267-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13412,7 +14244,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13422,12 +14254,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.978.730-7</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13445,20 +14277,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>18695.93</v>
+        <v>19986.68</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1079639-556-CM26</t>
+          <t>1079639-557-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13506,20 +14342,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>26992.25</v>
+        <v>18695.93</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1079639-555-CM26</t>
+          <t>1079639-556-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13567,20 +14407,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>42615.47</v>
+        <v>26992.25</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1057388-311-CM26</t>
+          <t>1079639-555-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13605,17 +14449,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.602.224-5</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13628,20 +14472,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>14588.45</v>
+        <v>42615.47</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1057506-4210-CM26</t>
+          <t>1057388-311-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13666,17 +14514,17 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>61.602.224-5</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13689,20 +14537,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>22080.78</v>
+        <v>14588.45</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1978-620-CM26</t>
+          <t>1057506-4210-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13722,22 +14574,22 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13750,20 +14602,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>54097.02</v>
+        <v>22080.78</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2170-646-CM26</t>
+          <t>1978-620-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13783,22 +14639,22 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13811,14 +14667,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>9000.120000000001</v>
+        <v>54097.02</v>
       </c>
     </row>
     <row r="220">
@@ -13872,7 +14732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13933,7 +14797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13994,7 +14862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14055,7 +14927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14116,7 +14992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14129,12 +15009,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1079659-257-CM26</t>
+          <t>1057541-532-SE26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14144,7 +15024,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -14154,17 +15034,17 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14177,20 +15057,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>55430.72</v>
+        <v>314652.47</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1529-188-CM26</t>
+          <t>2170-646-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14205,7 +15089,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -14215,17 +15099,17 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14238,20 +15122,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>52146.81</v>
+        <v>9000.120000000001</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1552-311-CM26</t>
+          <t>1529-188-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14276,17 +15164,17 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14299,14 +15187,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>38227.13</v>
+        <v>52146.81</v>
       </c>
     </row>
     <row r="228">
@@ -14360,7 +15252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14421,7 +15317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14434,7 +15334,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1705-425-CM26</t>
+          <t>1552-311-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14449,7 +15349,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -14459,17 +15359,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14482,20 +15382,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>23876.4</v>
+        <v>38227.13</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2085-524-CM26</t>
+          <t>1079659-257-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14510,7 +15414,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -14520,12 +15424,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14543,20 +15447,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>33753.22</v>
+        <v>55430.72</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>3111-21-CM26</t>
+          <t>584146-277-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14576,22 +15484,22 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.966.600-3</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14604,20 +15512,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>11486.62</v>
+        <v>302.59</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1079694-202-CM26</t>
+          <t>1371-27-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14642,17 +15554,17 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>75.971.200-5</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14665,20 +15577,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>37888.82</v>
+        <v>620.0599999999999</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1371-27-CM26</t>
+          <t>1705-425-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14703,17 +15619,17 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>75.971.200-5</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Comité de Seguros del Agro</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14726,20 +15642,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>620.0599999999999</v>
+        <v>23876.4</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>584146-277-CM26</t>
+          <t>3111-21-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14759,22 +15679,22 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.966.600-3</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14787,20 +15707,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>302.59</v>
+        <v>11486.62</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>889473-1013-CM26</t>
+          <t>2085-524-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14825,17 +15749,17 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14848,20 +15772,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>11231.36</v>
+        <v>33753.22</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>418-2073-CM26</t>
+          <t>1079694-202-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14886,17 +15814,17 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14909,20 +15837,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>37775.93</v>
+        <v>37888.82</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>4968-972-CM26</t>
+          <t>889473-1013-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14947,17 +15879,17 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -14970,20 +15902,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>6711.14</v>
+        <v>11231.36</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>4968-971-CM26</t>
+          <t>418-2073-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15008,17 +15944,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15031,20 +15967,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>4046.3</v>
+        <v>37775.93</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1191449-77-CM26</t>
+          <t>4968-972-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15069,17 +16009,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>60.905.006-3</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15092,20 +16032,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>9612.809999999999</v>
+        <v>6711.14</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>5701-85-CM26</t>
+          <t>4968-971-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15125,22 +16069,22 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15153,20 +16097,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>17664.4</v>
+        <v>4046.3</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>3347-91-CM26</t>
+          <t>1191449-77-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15191,12 +16139,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.101.036-2</t>
+          <t>60.905.006-3</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15214,20 +16162,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>5389.16</v>
+        <v>9612.809999999999</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>619-165-CM26</t>
+          <t>5701-85-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15247,17 +16199,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15275,20 +16227,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>206.2</v>
+        <v>17664.4</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1628-208-CM26</t>
+          <t>3347-91-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15313,17 +16269,17 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.101.036-2</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15336,20 +16292,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>16279.22</v>
+        <v>5389.16</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1057534-825-CM26</t>
+          <t>619-165-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15364,7 +16324,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -15374,17 +16334,17 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15397,20 +16357,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>18539.32</v>
+        <v>206.2</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1099834-79-CM26</t>
+          <t>1628-208-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15425,7 +16389,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -15435,17 +16399,17 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>62.000.640-8</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15458,25 +16422,29 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>5452.74</v>
+        <v>16279.22</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1627-886-SE26</t>
+          <t>1057534-825-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15496,17 +16464,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15530,13 +16498,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>80771.59</v>
+        <v>18539.32</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1681-472-CM26</t>
+          <t>1099834-79-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15561,17 +16529,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>62.000.640-8</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15584,25 +16552,29 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>35358.32</v>
+        <v>5452.74</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1383-186-CM26</t>
+          <t>1627-886-SE26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15617,22 +16589,22 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15645,20 +16617,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>9084.299999999999</v>
+        <v>80771.59</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1681-471-CM26</t>
+          <t>1681-472-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15706,20 +16682,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>48250.67</v>
+        <v>35358.32</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1000813-270-CM26</t>
+          <t>1383-186-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15739,22 +16719,22 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.999.040-4</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15767,20 +16747,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1744.88</v>
+        <v>9084.299999999999</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>617807-3650-CM26</t>
+          <t>1681-471-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15800,22 +16784,22 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15828,20 +16812,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>20453.6</v>
+        <v>48250.67</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>3951-148-CM26</t>
+          <t>1000813-270-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15866,17 +16854,17 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.999.040-4</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15889,20 +16877,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>12390.94</v>
+        <v>1744.88</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>898-2154-CM26</t>
+          <t>617807-3650-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15922,17 +16914,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15950,20 +16942,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>20720.42</v>
+        <v>20453.6</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1622-838-CM26</t>
+          <t>3951-148-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15988,17 +16984,17 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16011,20 +17007,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>23992.06</v>
+        <v>12390.94</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1681-482-CM26</t>
+          <t>898-2154-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16039,7 +17039,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -16049,17 +17049,17 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16072,20 +17072,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>109.65</v>
+        <v>20720.42</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1464-978-CM26</t>
+          <t>1622-838-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16100,7 +17104,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -16110,17 +17114,17 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.606.918-7</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16133,20 +17137,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>31609.82</v>
+        <v>23992.06</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>3787-40-CM26</t>
+          <t>1681-482-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16171,17 +17179,17 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16194,25 +17202,29 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>11359.35</v>
+        <v>109.65</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>5349-1302-CM26</t>
+          <t>4452-547-SE26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16232,17 +17244,17 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16255,20 +17267,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>63704.87</v>
+        <v>165633.96</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1057512-547-CM26</t>
+          <t>1464-978-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16293,17 +17309,17 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.607.004-5</t>
+          <t>61.606.918-7</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16316,20 +17332,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>16838.79</v>
+        <v>31609.82</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1057506-4235-CM26</t>
+          <t>3787-40-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16354,17 +17374,17 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16377,20 +17397,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>5421.72</v>
+        <v>11359.35</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1623-284-CM26</t>
+          <t>5349-1302-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16415,17 +17439,17 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16438,20 +17462,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>13023.25</v>
+        <v>63704.87</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>3970-25-CM26</t>
+          <t>1057512-547-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16476,17 +17504,17 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>61.607.004-5</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16499,74 +17527,277 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>29229.79</v>
+        <v>16838.79</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
+          <t>1057506-4235-CM26</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>61.602.194-K</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="n">
+        <v>5421.72</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>1623-284-CM26</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>61.602.142-7</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="n">
+        <v>13023.25</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>3970-25-CM26</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>60.505.000-k</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="n">
+        <v>29229.79</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
           <t>1702-408-CM26</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B267" t="inlineStr">
         <is>
           <t>2239-1-LR26</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
         <is>
           <t>61.606.605-6</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
+      <c r="G267" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
+      <c r="H267" t="inlineStr">
         <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M264" s="2" t="n">
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="n">
         <v>32525.97</v>
       </c>
     </row>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jun-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M267"/>
+  <dimension ref="A1:M266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2009,7 +2009,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1079689-227-CM26</t>
+          <t>3474-304-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>25126.3</v>
+        <v>901.71</v>
       </c>
     </row>
     <row r="26">
@@ -2464,7 +2464,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>889473-835-CM26</t>
+          <t>1079689-227-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2489,17 +2489,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>12832.64</v>
+        <v>25126.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3474-304-CM26</t>
+          <t>1465-220-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2554,17 +2554,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>901.71</v>
+        <v>14981.46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>812261-860-CM26</t>
+          <t>889473-835-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2619,17 +2619,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1238.24</v>
+        <v>12832.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1057461-832-CM26</t>
+          <t>3439-74-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2684,17 +2684,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1870.77</v>
+        <v>1974.09</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3439-74-CM26</t>
+          <t>812261-860-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1974.09</v>
+        <v>1238.24</v>
       </c>
     </row>
     <row r="37">
@@ -3179,7 +3179,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1465-220-CM26</t>
+          <t>1057461-832-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>14981.46</v>
+        <v>1870.77</v>
       </c>
     </row>
     <row r="44">
@@ -3374,7 +3374,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057370-331-CM26</t>
+          <t>1469-1489-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3394,22 +3394,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.602.040-4</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3433,13 +3433,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>15169.58</v>
+        <v>1648.23</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1469-1489-CM26</t>
+          <t>1057540-1431-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3459,22 +3459,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3498,13 +3498,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1648.23</v>
+        <v>79672.14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1057540-1431-CM26</t>
+          <t>1469-1478-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3524,22 +3524,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>79672.14</v>
+        <v>690.49</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1469-1478-CM26</t>
+          <t>643553-345-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3594,17 +3594,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>71.455.500-6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE SN JOAQUIN</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3628,13 +3628,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>690.49</v>
+        <v>7827.44</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1079969-105-CM26</t>
+          <t>1057370-331-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3659,17 +3659,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.944.800-6</t>
+          <t>61.602.040-4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>777.6</v>
+        <v>15169.58</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1623-239-CM26</t>
+          <t>1079969-105-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3724,17 +3724,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.944.800-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>13419.51</v>
+        <v>777.6</v>
       </c>
     </row>
     <row r="52">
@@ -4024,7 +4024,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>643553-345-CM26</t>
+          <t>1623-239-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4044,22 +4044,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>71.455.500-6</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE SN JOAQUIN</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>7827.44</v>
+        <v>13419.51</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1079969-111-CM26</t>
+          <t>1057415-2983-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4114,17 +4114,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.944.800-6</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>582.74</v>
+        <v>33184.73</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1057415-2983-CM26</t>
+          <t>2202-642-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4179,17 +4179,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>33184.73</v>
+        <v>19106.36</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2202-642-CM26</t>
+          <t>1079969-112-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4244,17 +4244,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.944.800-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4278,13 +4278,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>19106.36</v>
+        <v>1180.35</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1079969-112-CM26</t>
+          <t>1079969-111-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1180.35</v>
+        <v>582.74</v>
       </c>
     </row>
     <row r="61">
@@ -4479,7 +4479,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1511-690-CM26</t>
+          <t>1079969-107-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4504,17 +4504,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>61.944.800-6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>26089.52</v>
+        <v>2119.74</v>
       </c>
     </row>
     <row r="64">
@@ -4804,7 +4804,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1079969-107-CM26</t>
+          <t>1511-690-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4829,17 +4829,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.944.800-6</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2119.74</v>
+        <v>26089.52</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4343-197-CM26</t>
+          <t>4343-196-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>24838.24</v>
+        <v>396.8</v>
       </c>
     </row>
     <row r="70">
@@ -4999,7 +4999,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1079967-296-CM26</t>
+          <t>4343-197-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5024,17 +5024,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5058,13 +5058,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>4078.48</v>
+        <v>24838.24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4343-196-CM26</t>
+          <t>1079967-296-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5089,17 +5089,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>396.8</v>
+        <v>4078.48</v>
       </c>
     </row>
     <row r="73">
@@ -5194,7 +5194,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1079967-294-CM26</t>
+          <t>898-1913-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>15156.54</v>
+        <v>21916.09</v>
       </c>
     </row>
     <row r="75">
@@ -5389,7 +5389,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>898-1913-CM26</t>
+          <t>1079967-294-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5414,17 +5414,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>21916.09</v>
+        <v>15156.54</v>
       </c>
     </row>
     <row r="78">
@@ -5519,7 +5519,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5013-31-CM26</t>
+          <t>1661-346-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5544,17 +5544,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>65.455.650-4</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>594.45</v>
+        <v>16655.06</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1338-64-CM26</t>
+          <t>5013-31-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5609,17 +5609,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>60.901.011-8</t>
+          <t>65.455.650-4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>960.75</v>
+        <v>594.45</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1298356-36-CM26</t>
+          <t>1338-64-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5669,22 +5669,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>60.901.011-8</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>26448.29</v>
+        <v>960.75</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3431-104-CM26</t>
+          <t>1298356-36-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5734,22 +5734,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4921.05</v>
+        <v>26448.29</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1057422-368-CM26</t>
+          <t>3431-104-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5804,17 +5804,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5838,13 +5838,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>72368.35000000001</v>
+        <v>4921.05</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3530-65-CM26</t>
+          <t>1057422-368-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5869,17 +5869,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.943.600-8</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2220.01</v>
+        <v>72368.35000000001</v>
       </c>
     </row>
     <row r="85">
@@ -6169,7 +6169,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1661-346-CM26</t>
+          <t>3530-65-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6194,17 +6194,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>61.943.600-8</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>16655.06</v>
+        <v>2220.01</v>
       </c>
     </row>
     <row r="90">
@@ -6299,7 +6299,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3950-848-CM26</t>
+          <t>2013-936-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6319,22 +6319,22 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>11535.62</v>
+        <v>829.34</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3374-73-CM26</t>
+          <t>4173-168-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6384,22 +6384,22 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6423,13 +6423,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3273.71</v>
+        <v>1047.59</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4173-168-CM26</t>
+          <t>1057513-315-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6449,17 +6449,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>61.607.005-3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6488,13 +6488,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1047.59</v>
+        <v>21692.46</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>995118-82-CM26</t>
+          <t>3950-848-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6553,13 +6553,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>961</v>
+        <v>11535.62</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1057513-315-CM26</t>
+          <t>995118-82-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6584,17 +6584,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.607.005-3</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>21692.46</v>
+        <v>961</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2013-936-CM26</t>
+          <t>3374-76-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6644,22 +6644,22 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6683,13 +6683,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>829.34</v>
+        <v>6547.43</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>711-263-CM26</t>
+          <t>3950-783-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6714,17 +6714,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.212.000-5</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6748,13 +6748,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3273.72</v>
+        <v>5757.18</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1057389-2668-CM26</t>
+          <t>2205-86-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6779,17 +6779,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6813,13 +6813,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>76168.44</v>
+        <v>6414.95</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2205-86-CM26</t>
+          <t>3374-73-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>61.101.006-0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>6414.95</v>
+        <v>3273.71</v>
       </c>
     </row>
     <row r="100">
@@ -6949,7 +6949,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3950-783-CM26</t>
+          <t>711-263-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6974,17 +6974,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.212.000-5</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7008,13 +7008,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>5757.18</v>
+        <v>3273.72</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3374-76-CM26</t>
+          <t>1057389-2668-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7039,17 +7039,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.101.006-0</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7073,13 +7073,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>6547.43</v>
+        <v>76168.44</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2186-521-CM26</t>
+          <t>2140-514-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7104,17 +7104,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.606.607-2</t>
+          <t>61.602.274-1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>14193.42</v>
+        <v>205.36</v>
       </c>
     </row>
     <row r="104">
@@ -7404,7 +7404,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2140-514-CM26</t>
+          <t>2186-521-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7429,17 +7429,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.602.274-1</t>
+          <t>61.606.607-2</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>205.36</v>
+        <v>14193.42</v>
       </c>
     </row>
     <row r="109">
@@ -7534,7 +7534,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1692-392-CM26</t>
+          <t>1079694-184-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7559,17 +7559,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7593,13 +7593,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>13541.06</v>
+        <v>224.02</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2137-461-CM26</t>
+          <t>1692-392-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7624,17 +7624,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7658,13 +7658,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>13584.88</v>
+        <v>13541.06</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1079694-184-CM26</t>
+          <t>2137-461-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7689,17 +7689,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>224.02</v>
+        <v>13584.88</v>
       </c>
     </row>
     <row r="113">
@@ -8054,7 +8054,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1078177-493-CM26</t>
+          <t>3323-73-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8113,13 +8113,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>18654.71</v>
+        <v>899.8099999999999</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>619133-3106-CM26</t>
+          <t>5067-1490-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8144,17 +8144,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8178,13 +8178,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>27819.02</v>
+        <v>9887.219999999999</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>831-158-CM26</t>
+          <t>1057480-1651-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8204,22 +8204,22 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>61.602.123-0</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8243,13 +8243,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3650.81</v>
+        <v>77006.00999999999</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1078177-491-CM26</t>
+          <t>2062-32-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8274,17 +8274,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>60.902.051-2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -8308,13 +8308,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>7048.03</v>
+        <v>99.01000000000001</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1057480-1651-CM26</t>
+          <t>831-158-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8334,22 +8334,22 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.602.123-0</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hospital de Melipilla</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -8373,13 +8373,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>77006.00999999999</v>
+        <v>3650.81</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5067-1490-CM26</t>
+          <t>1078177-493-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8404,17 +8404,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>9887.219999999999</v>
+        <v>18654.71</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2062-32-CM26</t>
+          <t>619133-3106-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8469,17 +8469,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>60.902.051-2</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>99.01000000000001</v>
+        <v>27819.02</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1723-329-CM26</t>
+          <t>1078177-491-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8529,22 +8529,22 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8568,13 +8568,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>12672.11</v>
+        <v>7048.03</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3323-73-CM26</t>
+          <t>1723-329-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8594,22 +8594,22 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>899.8099999999999</v>
+        <v>12672.11</v>
       </c>
     </row>
     <row r="127">
@@ -8834,7 +8834,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2410-266-CM26</t>
+          <t>2755-209-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8854,22 +8854,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8893,13 +8893,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>28377.93</v>
+        <v>25896.02</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2755-209-CM26</t>
+          <t>2755-208-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8964,7 +8964,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2755-208-CM26</t>
+          <t>1199-137-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8989,17 +8989,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9023,13 +9023,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>25896.02</v>
+        <v>6105.48</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1199-137-CM26</t>
+          <t>3326-364-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9054,17 +9054,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9088,13 +9088,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>6105.48</v>
+        <v>224.42</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3326-364-CM26</t>
+          <t>5707-213-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>224.42</v>
+        <v>8895.809999999999</v>
       </c>
     </row>
     <row r="135">
@@ -9224,7 +9224,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>734-395-CM26</t>
+          <t>1079659-233-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9249,17 +9249,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -9283,13 +9283,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>37742.24</v>
+        <v>3118.43</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3949-241-CM26</t>
+          <t>734-395-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9348,13 +9348,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>10562.72</v>
+        <v>37742.24</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5707-213-CM26</t>
+          <t>3949-241-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9379,17 +9379,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>8895.809999999999</v>
+        <v>10562.72</v>
       </c>
     </row>
     <row r="139">
@@ -9484,7 +9484,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1950-1171-CM26</t>
+          <t>1274667-197-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9504,22 +9504,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.602.238-5</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9543,13 +9543,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>43367.05</v>
+        <v>15045.04</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1079659-233-CM26</t>
+          <t>1620-134-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9574,17 +9574,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>3118.43</v>
+        <v>16679.05</v>
       </c>
     </row>
     <row r="142">
@@ -9874,7 +9874,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1274667-197-CM26</t>
+          <t>1950-1171-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9894,22 +9894,22 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.238-5</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9933,13 +9933,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>15045.04</v>
+        <v>43367.05</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1620-134-CM26</t>
+          <t>4776-295-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9964,17 +9964,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>61.108.000-k</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>16679.05</v>
+        <v>741303.22</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4776-295-CM26</t>
+          <t>5769-160-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10024,17 +10024,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.108.000-k</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10063,13 +10063,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>741303.22</v>
+        <v>327.09</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5769-160-CM26</t>
+          <t>3544-119-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10094,17 +10094,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>327.09</v>
+        <v>1685.15</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3544-119-CM26</t>
+          <t>2580-206-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10159,17 +10159,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1685.15</v>
+        <v>280.27</v>
       </c>
     </row>
     <row r="151">
@@ -10264,7 +10264,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2580-206-CM26</t>
+          <t>2200-214-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10289,17 +10289,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.606.700-1</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>SERVICIO DE SALUD ACONCAGUA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -10323,13 +10323,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>280.27</v>
+        <v>78640.2</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2200-214-CM26</t>
+          <t>2755-210-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.606.700-1</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10388,13 +10388,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>78640.2</v>
+        <v>22243.94</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2755-210-CM26</t>
+          <t>707423-114-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10419,17 +10419,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>22243.94</v>
+        <v>112062.28</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>707423-114-CM26</t>
+          <t>2580-192-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10484,17 +10484,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -10518,13 +10518,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>112062.28</v>
+        <v>280.27</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2580-192-CM26</t>
+          <t>619-153-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>280.27</v>
+        <v>2372.69</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>619-153-CM26</t>
+          <t>362-341-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -10614,17 +10614,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10648,13 +10648,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2372.69</v>
+        <v>8926.379999999999</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>362-341-CM26</t>
+          <t>2202-687-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10679,17 +10679,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10713,13 +10713,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>8926.379999999999</v>
+        <v>321.48</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2202-687-CM26</t>
+          <t>1057476-599-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10744,17 +10744,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.608.003-2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>INSTITUTO PSIQUIATRICO DR JOSE HORWITZ BARAK</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10778,13 +10778,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>321.48</v>
+        <v>1900.75</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1057476-599-CM26</t>
+          <t>3765-530-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10809,17 +10809,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.608.003-2</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>INSTITUTO PSIQUIATRICO DR JOSE HORWITZ BARAK</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10843,13 +10843,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1900.75</v>
+        <v>10448.04</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3765-530-CM26</t>
+          <t>1057476-598-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10874,17 +10874,17 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.608.003-2</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>INSTITUTO PSIQUIATRICO DR JOSE HORWITZ BARAK</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10908,13 +10908,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>10448.04</v>
+        <v>2334.62</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1057476-598-CM26</t>
+          <t>722-68-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.608.003-2</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>INSTITUTO PSIQUIATRICO DR JOSE HORWITZ BARAK</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10973,13 +10973,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2334.62</v>
+        <v>416.91</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>722-68-CM26</t>
+          <t>377-257-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10999,22 +10999,22 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -11038,13 +11038,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>416.91</v>
+        <v>32931.05</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>722-67-CM26</t>
+          <t>707420-101-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11064,22 +11064,22 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -11103,13 +11103,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>431.8</v>
+        <v>14740.62</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>377-257-CM26</t>
+          <t>722-67-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11129,22 +11129,22 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -11168,13 +11168,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>32931.05</v>
+        <v>431.8</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>707420-101-CM26</t>
+          <t>1051765-515-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11199,17 +11199,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -11233,13 +11233,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>14740.62</v>
+        <v>789.6</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2045-208-CM26</t>
+          <t>4414-793-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11264,17 +11264,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -11298,13 +11298,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>10151.94</v>
+        <v>393.06</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1051765-515-CM26</t>
+          <t>732434-161-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11329,17 +11329,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>65.913.720-8</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -11363,13 +11363,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>789.6</v>
+        <v>26906.65</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2188-176-CM26</t>
+          <t>2704-1164-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11389,22 +11389,22 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.602.134-6</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -11428,13 +11428,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>20303.88</v>
+        <v>5727.5</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1260057-695-CM26</t>
+          <t>1079580-198-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11459,17 +11459,17 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.602.121-4</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -11493,13 +11493,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>39479.77</v>
+        <v>42850.89</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1079580-198-CM26</t>
+          <t>2333-333-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11524,17 +11524,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>69.130.300-4</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -11558,13 +11558,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>42850.89</v>
+        <v>2030.11</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2704-1164-CM26</t>
+          <t>2045-208-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11584,22 +11584,22 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11623,13 +11623,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>5727.5</v>
+        <v>10151.94</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>732434-161-CM26</t>
+          <t>2188-176-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11654,17 +11654,17 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>65.913.720-8</t>
+          <t>61.602.134-6</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11688,13 +11688,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>26906.65</v>
+        <v>20303.88</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2333-333-CM26</t>
+          <t>1260057-695-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11719,17 +11719,17 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>61.602.121-4</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11753,13 +11753,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2030.11</v>
+        <v>39479.77</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>4414-793-CM26</t>
+          <t>4469-482-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11774,27 +11774,27 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11818,13 +11818,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>393.06</v>
+        <v>1075.32</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>4469-482-CM26</t>
+          <t>4469-481-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1075.32</v>
+        <v>1182.85</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>4469-481-CM26</t>
+          <t>5911-124-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11909,22 +11909,22 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>70.819.400-K</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>TRIBUNAL CONSTITUCIONAL</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11948,13 +11948,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1182.85</v>
+        <v>62701.76</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>5911-124-CM26</t>
+          <t>707409-61-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11979,17 +11979,17 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>70.819.400-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>TRIBUNAL CONSTITUCIONAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -12013,13 +12013,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>62701.76</v>
+        <v>855.73</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>707409-61-CM26</t>
+          <t>1337362-34-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12044,12 +12044,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -12078,13 +12078,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>855.73</v>
+        <v>1268.08</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1337362-34-CM26</t>
+          <t>1368-28-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12104,22 +12104,22 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>75.980.060-5</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1268.08</v>
+        <v>18131.68</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1368-28-CM26</t>
+          <t>1665-10117-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12169,22 +12169,22 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>75.980.060-5</t>
+          <t>61.602.311-k</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>18131.68</v>
+        <v>9639.15</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1665-10117-CM26</t>
+          <t>3456-64-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12239,17 +12239,17 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.602.311-k</t>
+          <t>61.935.300-5</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -12273,13 +12273,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>9639.15</v>
+        <v>2263.83</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3456-64-CM26</t>
+          <t>1663-729-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12304,17 +12304,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.935.300-5</t>
+          <t>61.602.276-8</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -12338,7 +12338,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2263.83</v>
+        <v>420264.55</v>
       </c>
     </row>
     <row r="184">
@@ -12409,7 +12409,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1663-729-CM26</t>
+          <t>3431-109-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12434,17 +12434,17 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.602.276-8</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -12468,13 +12468,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>420264.55</v>
+        <v>4120.16</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3431-109-CM26</t>
+          <t>848-114-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12499,17 +12499,17 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>4120.16</v>
+        <v>3316.96</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>848-114-CM26</t>
+          <t>848-113-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12598,13 +12598,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>3316.96</v>
+        <v>61991.26</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>848-113-CM26</t>
+          <t>1079505-323-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12629,17 +12629,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -12663,13 +12663,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>61991.26</v>
+        <v>163.45</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1079505-323-CM26</t>
+          <t>926-65-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12689,22 +12689,22 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.959.700-1</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12728,13 +12728,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>163.45</v>
+        <v>996.08</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>926-65-CM26</t>
+          <t>1623-248-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12754,22 +12754,22 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.959.700-1</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12793,13 +12793,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>996.08</v>
+        <v>565.98</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1623-248-CM26</t>
+          <t>2705-927-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12824,17 +12824,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12858,13 +12858,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>565.98</v>
+        <v>5252.08</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2705-927-CM26</t>
+          <t>5155-138-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12889,17 +12889,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>60.504.000-4</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12923,13 +12923,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>5252.08</v>
+        <v>30092.43</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5155-138-CM26</t>
+          <t>1643-1352-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>60.504.000-4</t>
+          <t>61.602.122-2</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SERVICIO ELECTORAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE T</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12988,13 +12988,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>30092.43</v>
+        <v>27928.53</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1643-1352-CM26</t>
+          <t>1075956-7-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -13019,12 +13019,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.602.122-2</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE T</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>27928.53</v>
+        <v>116474.77</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1075337-8637-CM26</t>
+          <t>4474-579-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -13079,22 +13079,22 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>69.160.600-7</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -13118,13 +13118,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>36595.63</v>
+        <v>278.65</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>4474-579-CM26</t>
+          <t>5155-139-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13144,22 +13144,22 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>69.160.600-7</t>
+          <t>60.504.000-4</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -13183,13 +13183,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>278.65</v>
+        <v>3343.77</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>5155-139-CM26</t>
+          <t>5827-30-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13214,12 +13214,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>60.504.000-4</t>
+          <t>61.977.660-7</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO ELECTORAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13248,13 +13248,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>3343.77</v>
+        <v>508.25</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1075956-7-CM26</t>
+          <t>1075337-8637-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13279,17 +13279,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -13313,13 +13313,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>116474.77</v>
+        <v>36595.63</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5827-30-CM26</t>
+          <t>1157285-9-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13339,17 +13339,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.977.660-7</t>
+          <t>62.000.860-5</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>508.25</v>
+        <v>68061.39</v>
       </c>
     </row>
     <row r="200">
@@ -13449,7 +13449,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1157285-9-CM26</t>
+          <t>4106-10-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13469,17 +13469,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>62.000.860-5</t>
+          <t>65.480.540-7</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -13508,13 +13508,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>68061.39</v>
+        <v>551.72</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4106-10-CM26</t>
+          <t>1057402-6716-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13539,17 +13539,17 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>65.480.540-7</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -13573,13 +13573,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>551.72</v>
+        <v>9020.620000000001</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1057402-6716-CM26</t>
+          <t>2013-1021-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13604,17 +13604,17 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -13638,13 +13638,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>9020.620000000001</v>
+        <v>14320.04</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2013-1021-CM26</t>
+          <t>1057402-6715-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13664,22 +13664,22 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -13703,13 +13703,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>14320.04</v>
+        <v>2959.89</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1057402-6715-CM26</t>
+          <t>1157285-10-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13729,22 +13729,22 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>62.000.860-5</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13768,18 +13768,18 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2959.89</v>
+        <v>14363.31</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1157285-10-CM26</t>
+          <t>2859-586-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13789,27 +13789,27 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>62.000.860-5</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13833,13 +13833,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>14363.31</v>
+        <v>666.22</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2859-586-CM26</t>
+          <t>3876-129-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13864,17 +13864,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13898,13 +13898,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>666.22</v>
+        <v>5065.82</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>3876-129-CM26</t>
+          <t>3413-53-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13924,22 +13924,22 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>61.971.700-7</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13963,13 +13963,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>5065.82</v>
+        <v>1484.99</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3413-53-CM26</t>
+          <t>2046-296-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13994,17 +13994,17 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.971.700-7</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -14028,18 +14028,18 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1484.99</v>
+        <v>19947.01</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>652-173-CM26</t>
+          <t>1077908-117-SE26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -14059,17 +14059,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -14093,13 +14093,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>41622.72</v>
+        <v>445747.94</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2046-296-CM26</t>
+          <t>2138-267-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -14124,17 +14124,17 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>61.978.730-7</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -14158,18 +14158,18 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>19947.01</v>
+        <v>19986.68</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1077908-117-SE26</t>
+          <t>652-173-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -14189,17 +14189,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -14223,13 +14223,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>445747.94</v>
+        <v>41622.72</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2138-267-CM26</t>
+          <t>1057506-4210-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -14254,17 +14254,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.978.730-7</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -14288,7 +14288,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>19986.68</v>
+        <v>22080.78</v>
       </c>
     </row>
     <row r="214">
@@ -14554,7 +14554,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1057506-4210-CM26</t>
+          <t>1978-620-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14574,22 +14574,22 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -14613,13 +14613,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>22080.78</v>
+        <v>54097.02</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1978-620-CM26</t>
+          <t>2170-645-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14639,22 +14639,22 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -14678,13 +14678,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>54097.02</v>
+        <v>21863.31</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2170-645-CM26</t>
+          <t>900-646-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14709,12 +14709,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.979.910-0</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14743,13 +14743,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>21863.31</v>
+        <v>1813.02</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>900-646-CM26</t>
+          <t>1099402-301-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14774,12 +14774,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.979.910-0</t>
+          <t>62.000.620-3</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14808,13 +14808,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1813.02</v>
+        <v>16229.11</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1099402-301-CM26</t>
+          <t>2080-5899-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14834,22 +14834,22 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>62.000.620-3</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14873,13 +14873,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>16229.11</v>
+        <v>13304.02</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2080-5899-CM26</t>
+          <t>1557-226-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14899,22 +14899,22 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14938,18 +14938,18 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>13304.02</v>
+        <v>19750.96</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1557-226-CM26</t>
+          <t>1057541-532-SE26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14969,17 +14969,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -15003,18 +15003,18 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>19750.96</v>
+        <v>314652.47</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1057541-532-SE26</t>
+          <t>2170-646-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -15034,17 +15034,17 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -15068,13 +15068,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>314652.47</v>
+        <v>9000.120000000001</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2170-646-CM26</t>
+          <t>1529-188-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15089,7 +15089,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -15099,17 +15099,17 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -15133,13 +15133,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>9000.120000000001</v>
+        <v>52146.81</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1529-188-CM26</t>
+          <t>973153-3-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15164,17 +15164,17 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -15198,13 +15198,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>52146.81</v>
+        <v>546.1</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>973153-3-CM26</t>
+          <t>1070329-170-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15229,17 +15229,17 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -15263,13 +15263,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>546.1</v>
+        <v>13106.66</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1070329-170-CM26</t>
+          <t>1552-311-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15294,17 +15294,17 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -15328,13 +15328,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>13106.66</v>
+        <v>38227.13</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1552-311-CM26</t>
+          <t>1079659-257-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -15393,13 +15393,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>38227.13</v>
+        <v>55430.72</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1079659-257-CM26</t>
+          <t>584146-277-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15414,27 +15414,27 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>55430.72</v>
+        <v>302.59</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>584146-277-CM26</t>
+          <t>1371-27-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15484,22 +15484,22 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>75.971.200-5</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -15523,13 +15523,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>302.59</v>
+        <v>620.0599999999999</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1371-27-CM26</t>
+          <t>1705-425-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15554,17 +15554,17 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>75.971.200-5</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Comité de Seguros del Agro</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -15588,13 +15588,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>620.0599999999999</v>
+        <v>23876.4</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1705-425-CM26</t>
+          <t>1079694-202-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15619,17 +15619,17 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>23876.4</v>
+        <v>37888.82</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>3111-21-CM26</t>
+          <t>2085-524-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15684,17 +15684,17 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.966.600-3</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -15718,13 +15718,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>11486.62</v>
+        <v>33753.22</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2085-524-CM26</t>
+          <t>3111-21-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15749,17 +15749,17 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.966.600-3</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -15783,13 +15783,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>33753.22</v>
+        <v>11486.62</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1079694-202-CM26</t>
+          <t>889473-1013-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15814,17 +15814,17 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15848,13 +15848,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>37888.82</v>
+        <v>11231.36</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>889473-1013-CM26</t>
+          <t>3347-91-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15879,17 +15879,17 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.101.036-2</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15913,13 +15913,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>11231.36</v>
+        <v>5389.16</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>418-2073-CM26</t>
+          <t>4968-972-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15944,17 +15944,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15978,13 +15978,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>37775.93</v>
+        <v>6711.14</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>4968-972-CM26</t>
+          <t>4968-971-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -16043,13 +16043,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>6711.14</v>
+        <v>4046.3</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>4968-971-CM26</t>
+          <t>1191449-77-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16074,17 +16074,17 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>60.905.006-3</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -16108,13 +16108,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>4046.3</v>
+        <v>9612.809999999999</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1191449-77-CM26</t>
+          <t>5701-85-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16134,17 +16134,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>60.905.006-3</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -16173,13 +16173,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>9612.809999999999</v>
+        <v>17664.4</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5701-85-CM26</t>
+          <t>418-2073-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16199,22 +16199,22 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -16238,13 +16238,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>17664.4</v>
+        <v>37775.93</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>3347-91-CM26</t>
+          <t>619-165-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.101.036-2</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -16303,13 +16303,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>5389.16</v>
+        <v>206.2</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>619-165-CM26</t>
+          <t>1628-208-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16334,17 +16334,17 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>206.2</v>
+        <v>16279.22</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1628-208-CM26</t>
+          <t>1057534-825-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16389,7 +16389,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -16399,17 +16399,17 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -16433,13 +16433,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>16279.22</v>
+        <v>18539.32</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1057534-825-CM26</t>
+          <t>1099834-79-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16464,17 +16464,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>62.000.640-8</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -16498,18 +16498,18 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>18539.32</v>
+        <v>5452.74</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1099834-79-CM26</t>
+          <t>1627-886-SE26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-2-LR21</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -16529,17 +16529,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>62.000.640-8</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -16563,18 +16563,18 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>5452.74</v>
+        <v>80771.59</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1627-886-SE26</t>
+          <t>1681-472-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2239-2-LR21</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -16594,17 +16594,17 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -16628,13 +16628,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>80771.59</v>
+        <v>35358.32</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1681-472-CM26</t>
+          <t>1383-186-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16654,22 +16654,22 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -16693,13 +16693,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>35358.32</v>
+        <v>9084.299999999999</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1383-186-CM26</t>
+          <t>1681-471-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16719,22 +16719,22 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>9084.299999999999</v>
+        <v>48250.67</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1681-471-CM26</t>
+          <t>1000813-270-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16789,17 +16789,17 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.999.040-4</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -16823,13 +16823,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>48250.67</v>
+        <v>1744.88</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1000813-270-CM26</t>
+          <t>617807-3650-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16849,22 +16849,22 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.999.040-4</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -16888,13 +16888,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1744.88</v>
+        <v>20453.6</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>617807-3650-CM26</t>
+          <t>3951-148-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16914,22 +16914,22 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -16953,13 +16953,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>20453.6</v>
+        <v>12390.94</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3951-148-CM26</t>
+          <t>898-2154-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16984,17 +16984,17 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -17018,13 +17018,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>12390.94</v>
+        <v>20720.42</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>898-2154-CM26</t>
+          <t>1622-838-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17049,17 +17049,17 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -17083,13 +17083,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>20720.42</v>
+        <v>23992.06</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1622-838-CM26</t>
+          <t>1681-482-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -17114,17 +17114,17 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -17148,18 +17148,18 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>23992.06</v>
+        <v>109.65</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1681-482-CM26</t>
+          <t>4452-547-SE26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -17179,12 +17179,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -17213,18 +17213,18 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>109.65</v>
+        <v>165633.96</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>4452-547-SE26</t>
+          <t>1464-978-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.918-7</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -17278,13 +17278,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>165633.96</v>
+        <v>31609.82</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1464-978-CM26</t>
+          <t>3787-40-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17309,17 +17309,17 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.606.918-7</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -17343,13 +17343,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>31609.82</v>
+        <v>11359.35</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>3787-40-CM26</t>
+          <t>5349-1302-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17374,17 +17374,17 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -17408,13 +17408,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>11359.35</v>
+        <v>63704.87</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5349-1302-CM26</t>
+          <t>1057512-547-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17439,17 +17439,17 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.607.004-5</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -17473,13 +17473,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>63704.87</v>
+        <v>16838.79</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1057512-547-CM26</t>
+          <t>1057506-4235-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17504,12 +17504,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.607.004-5</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17538,13 +17538,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>16838.79</v>
+        <v>5421.72</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1057506-4235-CM26</t>
+          <t>1623-284-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17569,17 +17569,17 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -17603,13 +17603,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>5421.72</v>
+        <v>13023.25</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1623-284-CM26</t>
+          <t>3970-25-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17634,17 +17634,17 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -17668,13 +17668,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>13023.25</v>
+        <v>29229.79</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>3970-25-CM26</t>
+          <t>1702-408-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17699,17 +17699,17 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>61.606.605-6</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -17733,71 +17733,6 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>29229.79</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>1702-408-CM26</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>2239-1-LR26</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>61.606.605-6</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M267" s="2" t="n">
         <v>32525.97</v>
       </c>
     </row>
